--- a/tests/fixtures/manual_spill_cache/input_insert_inside_recalculate.xlsx
+++ b/tests/fixtures/manual_spill_cache/input_insert_inside_recalculate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\manual_spill_cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E6EAD61-2813-4DCF-9B96-C03D5C162ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD5BB484-7454-4CE9-A386-DEB59B3D4E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{57C8D3D3-EE1A-4DD5-B730-CB6F07387B76}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{C00782A1-D486-4261-961E-5B5412E44C82}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6AAB9D3-9C60-4616-8D29-1406425EAC11}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B598A40-3A34-4AA7-B1AA-4DAF93FE296E}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -475,7 +475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3139F85E-323A-4226-897F-A6A51C431FFD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EACDD9E4-B13C-4291-99DE-93CADA444FF3}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
